--- a/stories/arbres/ATOM-LAN.MOT.001-05.xlsx
+++ b/stories/arbres/ATOM-LAN.MOT.001-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Honorine est dans la cuisine. Papa pose un panier. Dedans, il y a une pomme. Une poire. Un bonnet. Une chaussette. Papa dit : on nomme. On classe. Les fruits ensemble. Les habits ensemble. La pomme, c'est un fruit. La poire, c'est un fruit. Honorine les met ensemble. Le bonnet, c'est un habit. La chaussette, c'est un habit. Papa dit : fruits, c'est une catégorie. Habits, c'est une catégorie. Honorine répète : catégorie. Elle pose les fruits. Elle pose les habits.</t>
+          <t>Honorine est dans la cuisine. Papa pose un panier. Dedans, il y a une pomme. Une poire. Un bonnet. Une chaussette. On nomme. On classe. Les fruits ensemble. Les habits ensemble. La pomme, c'est un fruit. La poire, c'est un fruit. Honorine les met ensemble. Le bonnet, c'est un habit. La chaussette, c'est un habit. Fruits, c'est une catégorie. Habits, c'est une catégorie. Honorine répète : catégorie. Elle pose les fruits. Elle pose les habits.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Honorine est dans la cuisine. Papa pose un panier. Dedans, il y a une pomme. Une poire. Un bonnet. Une chaussette.
+papa|On nomme. On classe.
+narrateur|Les fruits ensemble. Les habits ensemble. La pomme, c'est un fruit. La poire, c'est un fruit. Honorine les met ensemble. Le bonnet, c'est un habit. La chaussette, c'est un habit.
+papa|Fruits, c'est une catégorie. Habits, c'est une catégorie.
+narrateur|Honorine répète : catégorie. Elle pose les fruits. Elle pose les habits.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Honorine range pomme et bonnet. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1663,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Honorine a nommé. Elle a classé. Une catégorie pour les fruits. Une catégorie pour les habits.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1826,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Honorine croque la pomme. Papa plie le bonnet.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1993,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2033,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.MOT.001-05.xlsx
+++ b/stories/arbres/ATOM-LAN.MOT.001-05.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Honorine répète : catégorie. Elle pose les fruits. Elle pose les habits.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1503,7 @@
           <t>narrateur|Honorine range pomme et bonnet. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1668,6 +1675,7 @@
           <t>narrateur|Honorine a nommé. Elle a classé. Une catégorie pour les fruits. Une catégorie pour les habits.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1831,6 +1839,7 @@
           <t>narrateur|Honorine croque la pomme. Papa plie le bonnet.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1998,6 +2007,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2016,7 +2026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2040,6 +2050,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2241,6 +2265,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-LAN.MOT.001-05.xlsx
+++ b/stories/arbres/ATOM-LAN.MOT.001-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Honorine classe fruits et habits</t>
+          <t>La bouilloire et la pomme de Nina</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>La bouilloire chante. La pomme rouge de Nina brille dans le saladier. Elle nomme et met fruits et habits chacun ensemble.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Honorine est dans la cuisine. Papa pose un panier. Dedans, il y a une pomme. Une poire. Un bonnet. Une chaussette. On nomme. On classe. Les fruits ensemble. Les habits ensemble. La pomme, c'est un fruit. La poire, c'est un fruit. Honorine les met ensemble. Le bonnet, c'est un habit. La chaussette, c'est un habit. Fruits, c'est une catégorie. Habits, c'est une catégorie. Honorine répète : catégorie. Elle pose les fruits. Elle pose les habits.</t>
+          <t>La bouilloire commence un petit chant. La pomme rouge brille dans le saladier. Le soir entre par la fenêtre. Un lampadaire s'allume, tout loin. Un bonnet tricoté attend sur une chaise. Ça sent le thé, déjà, tout doux. Nina, tu entends la bouilloire ? Oui, papa. Elle chante. Le panier s'est mélangé. On range avant le thé. En ce moment, Nina tire une chaise. Les pieds de la chaise glissent un peu. Papa pose le panier près d'elle. Dedans, il y a une pomme. Une poire. Un bonnet. Une chaussette. La pomme est toute rouge. On nomme. On classe. Les fruits ensemble. Les habits ensemble. Nina prend la pomme. Elle est lisse et froide. Pomme. C'est un fruit. Oui. Mets-la dans le saladier. Nina pose la pomme dans le saladier. Elle prend la poire jaune. La poire a une petite queue. Poire. C'est un fruit aussi. Les fruits ensemble. C'est une catégorie. Nina met la poire avec la pomme. Elle prend le bonnet. Le bonnet est doux, tout chaud. Bonnet. C'est un habit. Oui. Pose-le sur la chaise. Nina pose le bonnet sur la chaise. Elle prend la chaussette. La chaussette a un petit motif. Chaussette. C'est un habit. Les habits ensemble. C'est une catégorie. Nina pose la chaussette sur la chaise. Catégorie. Fruits. Habits. Bravo, Nina. Tu as nommé. Tu as classé. Tu as mis ensemble. C'est du bon travail. Tu as fini de ranger le panier ? Oui, papa. Le saladier a les fruits. La chaise a les habits. La bouilloire chante plus fort, puis s'arrête. Le thé est prêt. On a rangé.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,11 +1324,72 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Honorine est dans la cuisine. Papa pose un panier. Dedans, il y a une pomme. Une poire. Un bonnet. Une chaussette.
-papa|On nomme. On classe.
-narrateur|Les fruits ensemble. Les habits ensemble. La pomme, c'est un fruit. La poire, c'est un fruit. Honorine les met ensemble. Le bonnet, c'est un habit. La chaussette, c'est un habit.
-papa|Fruits, c'est une catégorie. Habits, c'est une catégorie.
-narrateur|Honorine répète : catégorie. Elle pose les fruits. Elle pose les habits.</t>
+          <t>narrateur|La bouilloire commence un petit chant.
+narrateur|La pomme rouge brille dans le saladier.
+narrateur|Le soir entre par la fenêtre.
+narrateur|Un lampadaire s'allume, tout loin.
+narrateur|Un bonnet tricoté attend sur une chaise.
+narrateur|Ça sent le thé, déjà, tout doux.
+papa|Nina, tu entends la bouilloire ?
+enfant-f|Oui, papa.
+enfant-f|Elle chante.
+papa|Le panier s'est mélangé.
+papa|On range avant le thé.
+narrateur|En ce moment, Nina tire une chaise.
+narrateur|Les pieds de la chaise glissent un peu.
+narrateur|Papa pose le panier près d'elle.
+narrateur|Dedans, il y a une pomme.
+narrateur|Une poire.
+narrateur|Un bonnet.
+narrateur|Une chaussette.
+enfant-f|La pomme est toute rouge.
+papa|On nomme.
+papa|On classe.
+papa|Les fruits ensemble.
+papa|Les habits ensemble.
+narrateur|Nina prend la pomme.
+narrateur|Elle est lisse et froide.
+enfant-f|Pomme.
+enfant-f|C'est un fruit.
+papa|Oui.
+papa|Mets-la dans le saladier.
+narrateur|Nina pose la pomme dans le saladier.
+narrateur|Elle prend la poire jaune.
+narrateur|La poire a une petite queue.
+enfant-f|Poire.
+enfant-f|C'est un fruit aussi.
+papa|Les fruits ensemble.
+papa|C'est une catégorie.
+narrateur|Nina met la poire avec la pomme.
+narrateur|Elle prend le bonnet.
+narrateur|Le bonnet est doux, tout chaud.
+enfant-f|Bonnet.
+enfant-f|C'est un habit.
+papa|Oui.
+papa|Pose-le sur la chaise.
+narrateur|Nina pose le bonnet sur la chaise.
+narrateur|Elle prend la chaussette.
+narrateur|La chaussette a un petit motif.
+enfant-f|Chaussette.
+enfant-f|C'est un habit.
+papa|Les habits ensemble.
+papa|C'est une catégorie.
+narrateur|Nina pose la chaussette sur la chaise.
+enfant-f|Catégorie.
+enfant-f|Fruits.
+enfant-f|Habits.
+papa|Bravo, Nina.
+papa|Tu as nommé.
+papa|Tu as classé.
+papa|Tu as mis ensemble.
+papa|C'est du bon travail.
+papa|Tu as fini de ranger le panier ?
+enfant-f|Oui, papa.
+narrateur|Le saladier a les fruits.
+narrateur|La chaise a les habits.
+narrateur|La bouilloire chante plus fort, puis s'arrête.
+papa|Le thé est prêt.
+enfant-f|On a rangé.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1344,7 +1417,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Honorine range pomme et bonnet. Que fait-elle ?</t>
+          <t>Nina range pomme et bonnet. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1500,7 +1573,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Honorine range pomme et bonnet. Que fait-elle ?</t>
+          <t>narrateur|Nina range pomme et bonnet.
+narrateur|Que fait-elle ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1528,7 +1602,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Honorine a nommé. Elle a classé. Une catégorie pour les fruits. Une catégorie pour les habits.</t>
+          <t>Nina a nommé. Elle a classé. Une catégorie pour les fruits. Une catégorie pour les habits. Tu as mis ensemble. Bravo, Nina. C'est du bon travail. Les fruits sont où ? Dans le saladier. Et les habits ? Sur la chaise. Le soir est plus bleu, à la fenêtre. Le lampadaire brille, tout loin.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1672,7 +1746,19 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Honorine a nommé. Elle a classé. Une catégorie pour les fruits. Une catégorie pour les habits.</t>
+          <t>narrateur|Nina a nommé.
+narrateur|Elle a classé.
+narrateur|Une catégorie pour les fruits.
+narrateur|Une catégorie pour les habits.
+papa|Tu as mis ensemble.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+papa|Les fruits sont où ?
+enfant-f|Dans le saladier.
+papa|Et les habits ?
+enfant-f|Sur la chaise.
+narrateur|Le soir est plus bleu, à la fenêtre.
+narrateur|Le lampadaire brille, tout loin.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1700,7 +1786,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Honorine croque la pomme. Papa plie le bonnet.</t>
+          <t>Nina croque la pomme. Elle craque, tout clair. Tu aimes ? Oui, papa. Papa plie le bonnet. Il pose la chaussette sur le dossier. Les habits sont ensemble. Les fruits aussi. On boit le thé, tout doux ? Oui. La tasse est tiède entre les mains. Ça sent la vapeur, tout près. Tu as classé, puis tu croques. C'était un bon soir.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1836,7 +1922,20 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Honorine croque la pomme. Papa plie le bonnet.</t>
+          <t>narrateur|Nina croque la pomme.
+narrateur|Elle craque, tout clair.
+papa|Tu aimes ?
+enfant-f|Oui, papa.
+narrateur|Papa plie le bonnet.
+narrateur|Il pose la chaussette sur le dossier.
+papa|Les habits sont ensemble.
+enfant-f|Les fruits aussi.
+papa|On boit le thé, tout doux ?
+enfant-f|Oui.
+narrateur|La tasse est tiède entre les mains.
+narrateur|Ça sent la vapeur, tout près.
+papa|Tu as classé, puis tu croques.
+enfant-f|C'était un bon soir.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1864,7 +1963,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai nommé. J'ai classé. Bravo. Tu as fait du bon travail. La bouilloire s'est tue. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2004,7 +2103,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai nommé.
+enfant-f|J'ai classé.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|La bouilloire s'est tue.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2026,7 +2130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2064,6 +2168,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.MOT.001-05.xlsx
+++ b/stories/arbres/ATOM-LAN.MOT.001-05.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La bouilloire commence un petit chant. La pomme rouge brille dans le saladier. Le soir entre par la fenêtre. Un lampadaire s'allume, tout loin. Un bonnet tricoté attend sur une chaise. Ça sent le thé, déjà, tout doux. Nina, tu entends la bouilloire ? Oui, papa. Elle chante. Le panier s'est mélangé. On range avant le thé. En ce moment, Nina tire une chaise. Les pieds de la chaise glissent un peu. Papa pose le panier près d'elle. Dedans, il y a une pomme. Une poire. Un bonnet. Une chaussette. La pomme est toute rouge. On nomme. On classe. Les fruits ensemble. Les habits ensemble. Nina prend la pomme. Elle est lisse et froide. Pomme. C'est un fruit. Oui. Mets-la dans le saladier. Nina pose la pomme dans le saladier. Elle prend la poire jaune. La poire a une petite queue. Poire. C'est un fruit aussi. Les fruits ensemble. C'est une catégorie. Nina met la poire avec la pomme. Elle prend le bonnet. Le bonnet est doux, tout chaud. Bonnet. C'est un habit. Oui. Pose-le sur la chaise. Nina pose le bonnet sur la chaise. Elle prend la chaussette. La chaussette a un petit motif. Chaussette. C'est un habit. Les habits ensemble. C'est une catégorie. Nina pose la chaussette sur la chaise. Catégorie. Fruits. Habits. Bravo, Nina. Tu as nommé. Tu as classé. Tu as mis ensemble. C'est du bon travail. Tu as fini de ranger le panier ? Oui, papa. Le saladier a les fruits. La chaise a les habits. La bouilloire chante plus fort, puis s'arrête. Le thé est prêt. On a rangé.</t>
+          <t>La bouilloire commence un petit chant. La pomme rouge brille dans le saladier. Le soir entre par la fenêtre. Un lampadaire s'allume, tout loin. Un bonnet tricoté attend sur une chaise. Ça sent le thé, déjà, tout doux. Nina, tu entends la bouilloire ? Oui, papa. Elle chante. Le panier s'est mélangé. On range avant le thé. En ce moment, Nina tire une chaise. Les pieds de la chaise glissent un peu. Papa pose le panier près d'elle. Dedans, il y a une pomme. Une poire. Un bonnet. Une chaussette. La pomme est toute rouge. On nomme. On classe. Les fruits ensemble. Les habits ensemble. Nina prend la pomme. Elle est lisse et froide. Pomme. C'est un fruit. Oui. Mets-la dans le saladier. Nina pose la pomme dans le saladier. Elle prend la poire jaune. La poire a une petite queue. Poire. C'est un fruit aussi. Les fruits ensemble. C'est une catégorie. Nina met la poire avec la pomme. Elle prend le bonnet. Le bonnet est doux, tout chaud. Bonnet. C'est un habit. Oui. Pose-le sur la chaise. Nina pose le bonnet sur la chaise. Elle prend la chaussette. La chaussette a un petit motif. Chaussette. C'est un habit. Les habits ensemble. C'est une catégorie. Nina pose la chaussette sur la chaise. Catégorie. Fruits. Habits. Bravo, Nina. Tu as nommé. Tu as classé. Tu as mis ensemble. Tu as fini de ranger le panier ? Oui, papa. Le saladier a les fruits. La chaise a les habits. La bouilloire chante plus fort, puis s'arrête. Le thé est prêt. On a rangé.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Honorine est dans la cuisine. Papa pose un panier. Dedans, il y a une pomme. Une poire. Un bonnet. Une chaussette. Papa dit : on nomme. On classe. Les fruits ensemble. Les habits ensemble. La pomme, c'est un fruit. La poire, c'est un fruit. Honorine les met ensemble. Le bonnet, c'est un habit. La chaussette, c'est un habit. Papa dit : fruits, c'est une &lt;emphasis level="moderate"&gt;catégorie&lt;/emphasis&gt;. Habits, c'est une catégorie. Honorine répète : catégorie. Elle pose les fruits. Elle pose les habits.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La bouilloire commence un petit chant. La pomme rouge brille dans le saladier. Le soir entre par la fenêtre. Un lampadaire s'allume, tout loin. Un bonnet tricoté attend sur une chaise. Ça sent le thé, déjà, tout doux. Nina, tu entends la bouilloire ? Oui, papa. Elle chante. Le panier s'est mélangé. On range avant le thé. En ce moment, Nina tire une chaise. Les pieds de la chaise glissent un peu. Papa pose le panier près d'elle. Dedans, il y a une pomme. Une poire. Un bonnet. Une chaussette. La pomme est toute rouge. On nomme. On classe. Les fruits ensemble. Les habits ensemble. Nina prend la pomme. Elle est lisse et froide. Pomme. C'est un fruit. Oui. Mets-la dans le saladier. Nina pose la pomme dans le saladier. Elle prend la poire jaune. La poire a une petite queue. Poire. C'est un fruit aussi. Les fruits ensemble. C'est une catégorie. Nina met la poire avec la pomme. Elle prend le bonnet. Le bonnet est doux, tout chaud. Bonnet. C'est un habit. Oui. Pose-le sur la chaise. Nina pose le bonnet sur la chaise. Elle prend la chaussette. La chaussette a un petit motif. Chaussette. C'est un habit. Les habits ensemble. C'est une catégorie. Nina pose la chaussette sur la chaise. Catégorie. Fruits. Habits. Bravo, Nina. Tu as nommé. Tu as classé. Tu as mis ensemble. Tu as fini de ranger le panier ? Oui, papa. Le saladier a les fruits. La chaise a les habits. La bouilloire chante plus fort, puis s'arrête. Le thé est prêt. On a rangé.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1382,7 +1382,6 @@
 papa|Tu as nommé.
 papa|Tu as classé.
 papa|Tu as mis ensemble.
-papa|C'est du bon travail.
 papa|Tu as fini de ranger le panier ?
 enfant-f|Oui, papa.
 narrateur|Le saladier a les fruits.
@@ -1392,7 +1391,6 @@
 enfant-f|On a rangé.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1422,7 +1420,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Honorine range pomme et bonnet. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina range pomme et bonnet. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1577,7 +1575,6 @@
 narrateur|Que fait-elle ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1602,12 +1599,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nina a nommé. Elle a classé. Une catégorie pour les fruits. Une catégorie pour les habits. Tu as mis ensemble. Bravo, Nina. C'est du bon travail. Les fruits sont où ? Dans le saladier. Et les habits ? Sur la chaise. Le soir est plus bleu, à la fenêtre. Le lampadaire brille, tout loin.</t>
+          <t>Nina a nommé. Elle a classé. Une catégorie pour les fruits. Une catégorie pour les habits. Tu as mis ensemble. Bravo, Nina. Les fruits sont où ? Dans le saladier. Et les habits ? Sur la chaise. Le soir est plus bleu, à la fenêtre. Le lampadaire brille, tout loin.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Honorine a nommé. Elle a classé. Une &lt;emphasis level="moderate"&gt;catégorie&lt;/emphasis&gt; pour les fruits. Une catégorie pour les habits.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina a nommé. Elle a classé. Une catégorie pour les fruits. Une catégorie pour les habits. Tu as mis ensemble. Bravo, Nina. Les fruits sont où ? Dans le saladier. Et les habits ? Sur la chaise. Le soir est plus bleu, à la fenêtre. Le lampadaire brille, tout loin.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1752,7 +1749,6 @@
 narrateur|Une catégorie pour les habits.
 papa|Tu as mis ensemble.
 papa|Bravo, Nina.
-papa|C'est du bon travail.
 papa|Les fruits sont où ?
 enfant-f|Dans le saladier.
 papa|Et les habits ?
@@ -1761,7 +1757,6 @@
 narrateur|Le lampadaire brille, tout loin.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,7 +1786,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Honorine croque la pomme. Papa plie le bonnet.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina croque la pomme. Elle craque, tout clair. Tu aimes ? Oui, papa. Papa plie le bonnet. Il pose la chaussette sur le dossier. Les habits sont ensemble. Les fruits aussi. On boit le thé, tout doux ? Oui. La tasse est tiède entre les mains. Ça sent la vapeur, tout près. Tu as classé, puis tu croques. C'était un bon soir.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1938,7 +1933,6 @@
 enfant-f|C'était un bon soir.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1963,12 +1957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai nommé. J'ai classé. Bravo. Tu as fait du bon travail. La bouilloire s'est tue. L'histoire est finie.</t>
+          <t>J'ai nommé. J'ai classé. Bravo. La bouilloire s'est tue.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai nommé. J'ai classé. Bravo. La bouilloire s'est tue.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2106,12 +2100,9 @@
           <t>enfant-f|J'ai nommé.
 enfant-f|J'ai classé.
 papa|Bravo.
-papa|Tu as fait du bon travail.
-narrateur|La bouilloire s'est tue.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|La bouilloire s'est tue.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2130,7 +2121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2175,6 +2166,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.MOT.001-05.xlsx
+++ b/stories/arbres/ATOM-LAN.MOT.001-05.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Honorine, papa</t>
+          <t>Nina, papa</t>
         </is>
       </c>
     </row>
